--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C004.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C004.xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유해·위험물질 목록 작성 서식" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'유해·위험물질 목록 작성 서식'!$A$2:$O$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'유해·위험물질 목록 작성 서식'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'유해·위험물질 목록 작성 서식'!$A$1:$O$270</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +32,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="00CC0000"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -52,7 +57,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,12 +71,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCCCC"/>
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -98,18 +108,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -186,6 +199,30 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_REF_C004_1" displayName="T_REF_C004_1" ref="A3:O63" headerRowCount="1">
+  <autoFilter ref="A3:O63"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="화학물질"/>
+    <tableColumn id="2" name="CAS No"/>
+    <tableColumn id="3" name="분자식"/>
+    <tableColumn id="4" name="하한"/>
+    <tableColumn id="5" name="상한"/>
+    <tableColumn id="6" name="노출기준"/>
+    <tableColumn id="7" name="독성치"/>
+    <tableColumn id="8" name="인화점(℃)"/>
+    <tableColumn id="9" name="발화점(℃)"/>
+    <tableColumn id="10" name="증기압(20℃, mmHg)"/>
+    <tableColumn id="11" name="부식성유무"/>
+    <tableColumn id="12" name="이상반응유무"/>
+    <tableColumn id="13" name="일일사용량"/>
+    <tableColumn id="14" name="저장량"/>
+    <tableColumn id="15" name="비고"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -477,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.9" customWidth="1" min="1" max="1"/>
@@ -504,307 +541,1167 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>【수동 입력 전용】 계산 방향 미검증 — 수식 자동 생성 금지 (FORMULA_DIRECTION_UNVERIFIED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>화학물질</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>CAS No</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>분자식</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>하한</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>상한</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>노출기준</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>독성치</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>인화점(℃)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>발화점(℃)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>증기압(20℃, mmHg)</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>부식성유무</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>이상반응유무</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>일일사용량</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>저장량</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-    </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr"/>
+      <c r="O37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="4" t="inlineStr"/>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="4" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr"/>
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr"/>
+      <c r="O41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="4" t="inlineStr"/>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr"/>
+      <c r="O45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="4" t="inlineStr"/>
+      <c r="B46" s="4" t="inlineStr"/>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="4" t="inlineStr"/>
+      <c r="B47" s="4" t="inlineStr"/>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr"/>
+      <c r="O47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="4" t="inlineStr"/>
+      <c r="B48" s="4" t="inlineStr"/>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="4" t="inlineStr"/>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr"/>
+      <c r="O49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="4" t="inlineStr"/>
+      <c r="B50" s="4" t="inlineStr"/>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="4" t="inlineStr"/>
+      <c r="B51" s="4" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="4" t="inlineStr"/>
+      <c r="B52" s="4" t="inlineStr"/>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="4" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr"/>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr"/>
+      <c r="O53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="4" t="inlineStr"/>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="4" t="inlineStr"/>
+      <c r="B55" s="4" t="inlineStr"/>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="4" t="inlineStr"/>
+      <c r="B56" s="4" t="inlineStr"/>
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="4" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr"/>
+      <c r="N56" s="4" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="4" t="inlineStr"/>
+      <c r="B57" s="4" t="inlineStr"/>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr"/>
+      <c r="M57" s="4" t="inlineStr"/>
+      <c r="N57" s="4" t="inlineStr"/>
+      <c r="O57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="4" t="inlineStr"/>
+      <c r="B58" s="4" t="inlineStr"/>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr"/>
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr"/>
+      <c r="M59" s="4" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="4" t="inlineStr"/>
+      <c r="B60" s="4" t="inlineStr"/>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr"/>
+      <c r="M60" s="4" t="inlineStr"/>
+      <c r="N60" s="4" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr"/>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr"/>
+      <c r="M61" s="4" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr"/>
+      <c r="O61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="4" t="inlineStr"/>
+      <c r="B62" s="4" t="inlineStr"/>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr"/>
+      <c r="L62" s="4" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="4" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr"/>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr"/>
+      <c r="J63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr"/>
+      <c r="L63" s="4" t="inlineStr"/>
+      <c r="M63" s="4" t="inlineStr"/>
+      <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>주) ① 유해·위험물질은 제출대상 설비에서 제조 또는 취급하는 모든 화학물질을 기재합니다.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>② 증기압은 상온에서 증기압을 말합니다.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>③ 부식성 유무는 있으면 ○, 없으면 ×로 표시합니다.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>④ 이상반응 여부는 그 물질과 이상반응을 일으키는 물질과 그 조건(금수성 등)을 표시하고 필요시 별도로 작성합니다.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>⑤ 노출기준에는 시간가중평균노출기준(TWA)을 기재합니다.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>⑥ 독성치에는 LD50(경구, 쥐), LD50(경피, 쥐 또는 토끼) 또는 LC50(흡입, 4시간 쥐)을 기재합니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:O12"/>
-  <mergeCells count="7">
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="A16:O16"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A14:O14"/>
+  <mergeCells count="8">
+    <mergeCell ref="A69:O69"/>
+    <mergeCell ref="A65:O65"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A64:O64"/>
+    <mergeCell ref="A68:O68"/>
+    <mergeCell ref="A66:O66"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A67:O67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C004.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C004.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유해·위험물질 목록 작성 서식" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'유해·위험물질 목록 작성 서식'!$A$1:$O$270</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'유해·위험물질 목록 작성 서식'!$A$1:$O$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
